--- a/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA26EB00-82A8-49E3-8BA0-B369C77FB67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC4440E-1966-4F4A-A613-317DA90FF162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16680" yWindow="1620" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3810" yWindow="2175" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>key</t>
   </si>
@@ -67,10 +67,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>pickup</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Pick Up</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -152,6 +148,22 @@
   </si>
   <si>
     <t>Appear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pickup</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Turn On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>켜기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TurnOn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -502,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -558,13 +570,13 @@
         <v>20000</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -572,13 +584,13 @@
         <v>20001</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -586,13 +598,13 @@
         <v>20002</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -600,13 +612,13 @@
         <v>20003</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -614,13 +626,13 @@
         <v>20004</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -628,13 +640,13 @@
         <v>20005</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -642,13 +654,13 @@
         <v>20006</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -656,13 +668,13 @@
         <v>20007</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -670,13 +682,13 @@
         <v>20008</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -684,13 +696,27 @@
         <v>20009</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>30</v>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>20010</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC4440E-1966-4F4A-A613-317DA90FF162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D67F704-F4B6-4901-9840-AEF691772A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="2175" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14130" yWindow="1605" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>key</t>
   </si>
@@ -164,6 +164,17 @@
   </si>
   <si>
     <t>TurnOn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Access</t>
+  </si>
+  <si>
+    <t>Access</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접근</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -514,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -719,6 +730,20 @@
         <v>34</v>
       </c>
     </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>20011</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D67F704-F4B6-4901-9840-AEF691772A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44904A9B-4CCB-4CB3-8C5F-3A47788F18A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14130" yWindow="1605" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8055" yWindow="2505" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44904A9B-4CCB-4CB3-8C5F-3A47788F18A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A998FE4E-37A1-4699-B547-B436B5BA550C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8055" yWindow="2505" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7005" yWindow="3675" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>key</t>
   </si>
@@ -175,6 +175,17 @@
   </si>
   <si>
     <t>접근</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Update Software</t>
+  </si>
+  <si>
+    <t>Update Software</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소프트웨어 업데이트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -525,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -744,6 +755,20 @@
         <v>38</v>
       </c>
     </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>20012</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/InteractTextTable.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GametubeGD\Desktop\Github\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A998FE4E-37A1-4699-B547-B436B5BA550C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="3675" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7935" yWindow="3675" windowWidth="14895" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>key</t>
   </si>
@@ -186,13 +185,21 @@
   </si>
   <si>
     <t>소프트웨어 업데이트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Save</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -535,8 +542,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -769,6 +776,20 @@
         <v>41</v>
       </c>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>20013</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
